--- a/backend/data/attachments/wealth_保险金信托合作方案_4.xlsx
+++ b/backend/data/attachments/wealth_保险金信托合作方案_4.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="D2" t="n">
-        <v>16241</v>
+        <v>17219</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>351</v>
+        <v>213</v>
       </c>
       <c r="C3" t="n">
-        <v>464</v>
+        <v>270</v>
       </c>
       <c r="D3" t="n">
-        <v>4726</v>
+        <v>4191</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C4" t="n">
-        <v>282</v>
+        <v>722</v>
       </c>
       <c r="D4" t="n">
-        <v>629</v>
+        <v>948</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>267</v>
+        <v>722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
